--- a/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:07:47+00:00</t>
+    <t>2026-09-23T11:10:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:10:32+00:00</t>
+    <t>2026-09-23T12:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:07:40+00:00</t>
+    <t>2026-09-24T11:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:21:48+00:00</t>
+    <t>2026-09-24T12:14:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T12:14:38+00:00</t>
+    <t>2026-09-25T08:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/qaErrors/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T08:12:06+00:00</t>
+    <t>2026-10-05T09:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
